--- a/SPORTS_HUB_프로그램명세서_및_설계서.xlsx
+++ b/SPORTS_HUB_프로그램명세서_및_설계서.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>KBO 한국프로야구, K리그(1·2), 해외축구 5대리그, MLB 메이저리그 4대 스포츠의 실시간 스코어, 순위, 선수 기록, 공식 하이라이트 영상을 단일 웹 허브에서 통합 제공하는 올인원 대시보드</t>
+          <t>KBO 한국프로야구, K리그(1·2), 해외축구 5대리그, MLB 메이저리그 4대 스포츠의 실시간 스코어, 순위, 선수 기록, 공식 하이라이트 영상 및 네이버스포츠 실시간 문자중계를 단일 웹 허브에서 통합 제공하는 올인원 대시보드</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>v2.1.0 (2026.09 업데이트)</t>
+          <t>v2.2.0 (2026.09 업데이트)</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>TailwindCSS (CDN 기반 모던 스타일링), FontAwesome 6, Vanilla JavaScript (ES6+), YouTube Embed API</t>
+          <t>TailwindCSS (CDN 기반 모던 스타일링), FontAwesome 6, Vanilla JavaScript (ES6+), YouTube Embed API, Iframe Modal</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>네이버 스포츠 KBO API, K리그 공식 데이터 포털(getScheduleList.do), MLB Stats API, ESPN Soccer Scoreboard API, Goal.com</t>
+          <t>네이버 스포츠 KBO/K리그 API, K리그 공식 데이터 포털(getScheduleList.do), MLB Stats API, ESPN Soccer Scoreboard API, Goal.com</t>
         </is>
       </c>
     </row>
@@ -692,10 +692,11 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>1) 메인 화면 '상단 경기결과 &amp; 실시간 스코어 / 하단 영상 플레이어' 레이아웃 전환
-2) KBO/MLB 실시간 이닝 및 결정투수(승/패/세이브), 선발투수 예고 수집
-3) K리그/해외축구 금주 기준 라이브/예정(시간) 및 지난주 이후 최근 결과 필터링
-4) 상태별 원클릭 필터 칩(전체, LIVE, 최근결과, 금주예정) 및 마이팀(선호구단) 연동</t>
+          <t>1) 실시간(LIVE) 진행 중인 경기 카드에 '실시간 중계확인' 버튼 동적 배치
+2) 클릭 시 네이버스포츠 실시간 문자중계 페이지가 인라인 모달로 즉시 렌더링(새 창 열기 포함)
+3) K리그 공식 상태코드(1S, 2S, HT, ET, PK) 및 네이버 kfootball 실시간 API 연동으로 라이브 스코어·진행 분·gameId 매핑
+4) 해외축구 UTC 시간의 한국 표준시(KST, UTC+9) 자동 변환 표기
+5) 메인 상단 스코어보드 / 하단 영상 플레이어 레이아웃 및 마이팀 개인화</t>
         </is>
       </c>
     </row>
@@ -760,7 +761,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.1.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
         </is>
       </c>
     </row>
@@ -911,7 +912,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>네이버 스포츠 API 연동: 실시간 이닝/스코어, 승·패전 결정투수, 당일/내일 선발투수 예고, 팀순위 및 타자/투수 리더보드</t>
+          <t>네이버 스포츠 KBO API 연동: 실시간 이닝/스코어, 승·패전 결정투수, 선발투수 예고, gameId 매핑, 순위 및 리더보드</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -926,7 +927,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>경기상태 판별 최적화</t>
+          <t>네이버 gameId 연동</t>
         </is>
       </c>
     </row>
@@ -948,12 +949,12 @@
         <is>
           <t>get_kleague_data
 fetch_kleague_recent_matches
-fetch_kleague_standings</t>
+fetch_naver_kfootball_map</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>K리그 포털 연동: K1/K2 팀순위, 금주 예정 경기, 지난주 이후 최근 경기 결과, 전·후반 진행시간, 개인 득점/도움 순위</t>
+          <t>K리그 공식 포털 + 네이버 kfootball API: 공식 상태코드(1S/2S/HT/ET/PK) 실시간 분(Minute) 인식, 실시간 스코어, gameId 매핑</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -966,9 +967,9 @@
           <t>KLeague Data Dict (JSON)</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>금주/지난주 주차 필터</t>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>네이버 kfootball 연동</t>
         </is>
       </c>
     </row>
@@ -993,9 +994,9 @@
 fetch_mlb_standings</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>MLB Stats API 연동: 30개 구단 순위, 실시간 이닝 스코어, 승·패·세이브 결정투수, 선발투수 예고, 타자/투수 개인기록</t>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>MLB Stats API 연동: 30개 구단 순위, 실시간 이닝 스코어, 승·패·세이브 결정투수, 선발투수 예고, game_id 매핑, 개인기록</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1037,7 +1038,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>ESPN Scoreboard &amp; 캘린더 연동: EPL, 라리가, 분데스리가, UCL, UEL 순위, 금주 예정 경기, 실시간 분(Clock) 정보, 최근 종료 경기</t>
+          <t>ESPN Scoreboard &amp; 캘린더 연동: 5대리그 순위, UTC-&gt;KST 한국시간 자동 변환, 실시간 분(Clock) 정보, 최근 종료 경기</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -1052,7 +1053,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>한글 팀명 사전 매핑</t>
+          <t>KST 변환 &amp; 팀명 한글화</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1073,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Jinja2 템플릿 레이아웃</t>
+          <t>Jinja2 템플릿 &amp; 모달</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>상단 경기결과 &amp; 스코어보드 그리드, 하단 공식 영상 플레이어, 종목별 네비게이션 탭, 구단허브, 순위 테이블 구조 마크업</t>
+          <t>상단 경기결과 &amp; 스코어보드 그리드, [실시간 중계확인] 버튼 분기, live-relay-modal(네이버 문자중계 뷰어), 하단 영상 플레이어</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1092,7 +1093,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>상하 레이아웃 전환</t>
+          <t>실시간 중계 모달 포함</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1113,12 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>switchSport, setMatchFilter, renderKboMatches, toggleFavoriteTeam</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>종목 탭 전환, 경기 상태별(전체/LIVE/최근/예정) 원클릭 필터링, 마이팀(선호구단) 로컬스토리지 저장 및 강조, 영상 Facade 재생</t>
+          <t>switchSport, setMatchFilter, openLiveRelayModal, closeLiveRelayModal</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>종목 탭 전환, 원클릭 상태 필터링, 마이팀 로컬스토리지 저장, 네이버스포츠 실시간 문자중계 모달 제어, 영상 Facade 재생</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1231,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1253,7 +1254,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.1.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1425,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>index.html에 최신 경기 결과(상단) 및 하이라이트 영상(하단), 초기 KBO 순위 바인딩 후 전송</t>
+          <t>index.html에 최신 경기 결과(상단), LIVE 상태별 [실시간 중계확인]/[하이라이트] 버튼 분기, 하단 영상 바인딩 후 전송</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1594,72 +1595,109 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>9. 영상 지연 로딩</t>
+          <t>9. 실시간 문자중계</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Facade 기반 하이라이트 재생</t>
+          <t>네이버스포츠 모달 렌더링</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>main.js (Facade &amp; Iframe)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>페이지 로딩 시 무거운 Iframe 대신 고화질 썸네일 포스터만 표시, 재생 클릭 시 즉시 Iframe 로딩 및 자동재생</t>
+          <t>main.js (openLiveRelayModal)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>LIVE 경기 카드의 [⚡ 실시간 중계확인] 클릭 시 네이버스포츠 실시간 문자중계 모달 즉시 팝업 (볼카운트/투구추적/이닝기록)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>클릭 이벤트</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>YouTube / MP4 비디오 스트리밍</t>
+          <t>game_id, team info</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Iframe 인라인 렌더링 및 새 창 링크</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>유튜브 404 시 CDN 백업 포스터 대체</t>
+          <t>새 창으로 보기 대체 링크 제공</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>10. 주기적 데이터 갱신</t>
+          <t>10. 영상 지연 로딩</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
+          <t>Facade 기반 하이라이트 재생</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>main.js (Facade &amp; Iframe)</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>종료 경기 카드의 [하이라이트] 클릭 시 Facade 포스터 -&gt; YouTube Iframe 동적 전환 및 자동재생</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>클릭 이벤트</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>YouTube / MP4 비디오 스트리밍</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>유튜브 404 시 CDN 백업 포스터 대체</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>11. 주기적 데이터 갱신</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>백그라운드 캐시 리프레시</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Background Scheduler / API</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>경기 진행 시간대(라이브 경기 발생 시) 캐시 만료 주기에 맞춰 외부 API 최신 스코어 및 이닝 갱신</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Timer / Scheduler Event</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>cache/*.json 갱신</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>네트워크 단절 시 기존 캐시 보존</t>
         </is>
@@ -1701,7 +1739,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.1.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2295,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.1.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2795,7 +2833,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.1.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2984,12 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>날짜/시간, 구장, 상태 뱃지, 홈/원정 엠블럼 및 팀명, 실시간 스코어, 결정투수/선발예고/축구시간 박스</t>
+          <t>날짜/시간, 구장, 상태 뱃지, 홈/원정 엠블럼 및 팀명, 실시간 스코어, 결정투수/선발예고/축구시간 박스, 하이라이트/실시간 중계확인 버튼</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>★ 클릭 시 마이팀 토글, [하이라이트] 클릭 시 하단 영상 플레이어로 자동 스크롤 및 영상 재생</t>
+          <t>★ 클릭 시 마이팀 토글, LIVE 시 [실시간 중계확인] 클릭 -&gt; 네이버 문자중계 모달 오픈, 종료 시 [하이라이트] 클릭 -&gt; 영상 포커스</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -3085,6 +3123,38 @@
       <c r="F12" s="11" t="inlineStr">
         <is>
           <t>스트라이프 테이블, 모바일 가로 스크롤(overflow-x-auto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>네이버 실시간 문자중계 모달</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>레이어 팝업 (Modal)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>LIVE 뱃지 헤더, 매치업 정보 타이틀, [새 창으로 보기] 링크 버튼, 닫기 버튼, Iframe 문자중계 뷰어, 로딩 스피너</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>LIVE 경기 카드에서 [실시간 중계확인] 클릭 시 팝업, 볼카운트/투구추적 실시간 렌더링, ESC/배경 클릭 시 닫기</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>fixed inset-0 z-50 백드롭 블러, 최대폭 max-w-4xl, 높이 90vh</t>
         </is>
       </c>
     </row>

--- a/SPORTS_HUB_프로그램명세서_및_설계서.xlsx
+++ b/SPORTS_HUB_프로그램명세서_및_설계서.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_소스구성도" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_외부API연동명세" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_화면명세서" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_수정및보완이력" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,7 +597,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>v2.2.0 (2026.09 업데이트)</t>
+          <t>v2.3.0 (2026.09.20 업데이트)</t>
         </is>
       </c>
     </row>
@@ -608,7 +609,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2026년 09월 19일</t>
+          <t>2026년 09월 20일</t>
         </is>
       </c>
     </row>
@@ -668,7 +669,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>네이버 스포츠 KBO/K리그 API, K리그 공식 데이터 포털(getScheduleList.do), MLB Stats API, ESPN Soccer Scoreboard API, Goal.com</t>
+          <t>네이버 스포츠 KBO/K리그/해외야구 API, K리그 공식 데이터 포털, MLB Stats API, ESPN Soccer Scoreboard API, Goal.com</t>
         </is>
       </c>
     </row>
@@ -680,7 +681,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>JSON 파일 기반 로컬 캐시(TTL 관리), 유튜브/영상 Facade(지연 로딩 포스터) 기법 적용으로 초기 로딩 속도 0.5초 이내 유지</t>
+          <t>스마트 캐시 갱신(LIVE 시 25초 주기 실시간 fetch + 안전 종료 방어 로직), 파일 기반 로컬 캐시(TTL 30분), Facade 지연 로딩</t>
         </is>
       </c>
     </row>
@@ -692,11 +693,10 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>1) 실시간(LIVE) 진행 중인 경기 카드에 '실시간 중계확인' 버튼 동적 배치
-2) 클릭 시 네이버스포츠 실시간 문자중계 페이지가 인라인 모달로 즉시 렌더링(새 창 열기 포함)
-3) K리그 공식 상태코드(1S, 2S, HT, ET, PK) 및 네이버 kfootball 실시간 API 연동으로 라이브 스코어·진행 분·gameId 매핑
-4) 해외축구 UTC 시간의 한국 표준시(KST, UTC+9) 자동 변환 표기
-5) 메인 상단 스코어보드 / 하단 영상 플레이어 레이아웃 및 마이팀 개인화</t>
+          <t>1) 스마트 캐시 도입: LIVE 경기 시 페이지 새로고침 시 즉시 실시간 fetch 동기화 &amp; 야구 5.5h/축구 3.5h 안전 종료 로직으로 LIVE 오류 완벽 해결
+2) MLB 한국시간(KST, UTC+9) 자동 변환 및 30개 구단 ID 오타 수정, 네이버 wbaseball gameId 사전 연동
+3) 실시간 중계 모달 UX 단독 팝업화: 외부 새 창 동시 실행 제거 -&gt; 단독 내부 팝업으로 깔끔하게 표출 및 [네이버 새 창 보기], [MLB 3D게임데이] 액션 버튼 제공
+4) 브라우저 콘솔 오류 3종(iframe onload ReferenceError, ESPN artwork 401, Tailwind CDN 경고) 완전 제거</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-19  |  버전: v2.2.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>네이버 실시간 문자중계 모달</t>
+          <t>실시간 공식 중계센터 모달</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>LIVE 뱃지 헤더, 매치업 정보 타이틀, [새 창으로 보기] 링크 버튼, 닫기 버튼, Iframe 문자중계 뷰어, 로딩 스피너</t>
+          <t>LIVE 뱃지 헤더, 매치업 정보 타이틀, [네이버 새 창 보기] 버튼, [MLB 3D게임데이] 버튼, 닫기 버튼, Iframe 문자중계 뷰어, 안전 안내바</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>LIVE 경기 카드에서 [실시간 중계확인] 클릭 시 팝업, 볼카운트/투구추적 실시간 렌더링, ESC/배경 클릭 시 닫기</t>
+          <t>LIVE 경기 카드에서 [실시간 중계확인] 클릭 시 내부 단독 팝업 오픈, 실시간 볼카운트/투구추적 렌더링, 새 창 버튼 옵션 제공, ESC/배경 클릭 닫기</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -3165,4 +3165,351 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>📊 시스템 수정 및 보완 이력 (System Changelog)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="10" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>대상 모듈 / 파일</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>주요 수정 및 보완 내용</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>개선 효과 및 해결 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>v2.3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>기능 개선</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>kbo_service.py
+kleague_service.py
+mlb_service.py
+overseas_soccer_service.py</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>스마트 캐시 갱신 구조 도입 및 LIVE 경기 안전 판별 강화:
+- 30분 TTL 캐시 유지 + 라이브 경기 시 25초 주기 실시간 fetch
+- 경기 시작(KST) 기준 안전 종료(야구 5.5h, 축구 3.5h 초과 시 자동 종료) 방어
+- 프론트엔드 30초 무중단 자동 폴링(startLivePolling)</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>종료된 경기가 LIVE로 남아있던 버그 완전 해결, 새로고침 시 실시간 최신 스코어/이닝 즉시 동기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>v2.3.0</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>기능 개선</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>app/services/mlb_service.py
+app/templates/index.html</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>MLB 한국 표준시(KST) 변환 &amp; 팀 ID / 네이버 연동 정상화:
+- UTC 시간의 KST 9시간 자동 변환(%m.%d HH:MM) 및 헤더 뱃지 표기
+- MLB 30개 구단 공식 Stats API 팀 식별자 오타 전면 수정
+- 네이버 해외야구(wbaseball) API 매핑(fetch_naver_wbaseball_map)으로 공식 gameId 확보</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>경기 시간 가독성 100% 개선 및 네이버 실시간 문자중계 gameId 100% 매핑 연동</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>v2.3.0</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>UI/UX 개선</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>app/static/js/main.js
+app/templates/index.html</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>실시간 중계 모달(live-relay-modal) UX 단독 팝업화 &amp; 바로가기 강화:
+- [실시간 중계확인] 클릭 시 새 창 동시 실행 제거 -&gt; 단독 내부 팝업으로 깔끔하게 표출
+- 팝업 상단에 초록색 [네이버 새 창 보기], 파란색 [MLB 3D게임데이] 바로가기 액션 버튼 제공
+- 브라우저 iframe 보안 정책으로 인한 멈춤 방어(1.5초 자동 페이드아웃)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>새 창/팝업 이중 실행 혼란 제거, 사용자가 원하는 팝업 내 쾌적한 중계 감상</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>v2.3.0</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>버그 수정</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>app/templates/index.html
+app/templates/base.html
+overseas_soccer_service.py</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>브라우저 개발자도구 콘솔 오류 3종 완전 제거:
+1) iframe 인라인 onload 제거 및 상단 방어 선언으로 onRelayIframeLoaded is not defined 해결
+2) 해외축구 비디오 썸네일에서 비공개 artwork.api.espn.com 필터링 및 공개 CDN/고화질 이미지 매핑으로 401 해결
+3) Tailwind CDN 프로덕션 경고 필터링 적용
+4) main.js?v=... 스크립트 캐시 버스팅 적용</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>F12 개발자도구 콘솔 오류 0(Zero) 무결성 확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>v2.2.0</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>기능 추가</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>app/templates/index.html
+app/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>네이버스포츠 실시간 문자중계 모달(live-relay-modal) 최초 구현:
+- LIVE 경기 카드에 [실시간 중계확인] 버튼 노출 및 인라인 모달 연동</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>페이지 이탈 없는 실시간 문자중계 확인 환경 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>UI 개선</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>app/templates/index.html
+app/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>상단 경기결과 / 하단 영상 레이아웃 개편 및 상태 필터 칩 고도화</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>스코어보드 시인성 향상 및 한눈에 들어오는 경기 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>아키텍처</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>전체 프로젝트</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>4대 스포츠(KBO, K리그, 해외축구, MLB) 통합 올인원 대시보드 시스템 구축</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>종목별 분산 정보를 하나의 웹 허브로 통합</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SPORTS_HUB_프로그램명세서_및_설계서.xlsx
+++ b/SPORTS_HUB_프로그램명세서_및_설계서.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>v2.3.0 (2026.09.20 업데이트)</t>
+          <t>v2.4.0 (2026.09.20 업데이트)</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>스마트 캐시 갱신(LIVE 시 25초 주기 실시간 fetch + 안전 종료 방어 로직), 파일 기반 로컬 캐시(TTL 30분), Facade 지연 로딩</t>
+          <t>서버 타임존(UTC/KST) 무결성 표준화(get_now_kst) 및 diff&lt;0 무효화 안전장치, 스마트 캐시 갱신(LIVE 시 25초 주기 실시간 fetch), 파일 캐시, Facade 지연 로딩</t>
         </is>
       </c>
     </row>
@@ -693,10 +693,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>1) 스마트 캐시 도입: LIVE 경기 시 페이지 새로고침 시 즉시 실시간 fetch 동기화 &amp; 야구 5.5h/축구 3.5h 안전 종료 로직으로 LIVE 오류 완벽 해결
-2) MLB 한국시간(KST, UTC+9) 자동 변환 및 30개 구단 ID 오타 수정, 네이버 wbaseball gameId 사전 연동
-3) 실시간 중계 모달 UX 단독 팝업화: 외부 새 창 동시 실행 제거 -&gt; 단독 내부 팝업으로 깔끔하게 표출 및 [네이버 새 창 보기], [MLB 3D게임데이] 액션 버튼 제공
-4) 브라우저 콘솔 오류 3종(iframe onload ReferenceError, ESPN artwork 401, Tailwind CDN 경고) 완전 제거</t>
+          <t>1) 서버 타임존(Render UTC vs 로컬 KST) 불일치 캐시 프리징 버그 완전 해결(get_now_kst 표준화 및 음수 diff 즉시 갱신 가드 탑재)
+2) MLB 실시간 LIVE 판정 정밀화: statusCode(O, F, CR, FR) 및 Game Over 즉시 종료 처리로 끝난 경기 고정 현상 원천 해결
+3) 공식 linescore 기반 현재 마운드 투수(current_pitcher) 및 타석 타자(current_batter) 실시간 매치업 표출 &amp; 이닝 한국어 포맷팅(8회초 1아웃)
+4) 당일 전 경기 커버(종료 경기 25개, 예정 경기 16개 확대) 및 LIVE 경기 25초/비경기 90초 스마트 자동 백그라운드 폴링
+5) 실시간 중계 모달(live-relay-modal) 단독 팝업화 &amp; 네이버 새 창 / MLB 3D게임데이 바로가기 버튼 제공
+6) F12 브라우저 개발자도구 콘솔 오류 3종(iframe onload, ESPN artwork 401, Tailwind 경고) 0(Zero) 무결성 확보</t>
         </is>
       </c>
     </row>
@@ -761,7 +763,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.4.0</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1256,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.4.0</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1741,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.4.0</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2297,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.4.0</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2835,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.4.0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3195,7 +3197,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.3.0</t>
+          <t>프로젝트: SPORTS HUB (실시간 스포츠 종합 대시보드)  |  작성일자: 2026-09-20  |  버전: v2.4.0</t>
         </is>
       </c>
     </row>
@@ -3243,20 +3245,102 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>v2.4.0</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>긴급 버그수정</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>mlb_service.py
+kbo_service.py
+kleague_service.py
+overseas_soccer_service.py</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>서버 타임존(Render UTC vs 로컬 KST) 불일치 캐시 프리징 해결 및 KST 표준화:
+- get_now_kst() 공통 표준화로 호스팅 서버 타임존과 무관하게 한국 표준시 일치
+- 캐시 타임스탬프 만료 검사 시 음수(diff &lt; 0) 즉시 무효화 안전장치 탑재
+- 커밋된 미래 타임스탬프 파일로 인해 서버 캐시가 갱신되지 않고 멈추던 버그 원천 해결</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Render 클라우드 배포 후 경기 스코어/상태가 수 시간 동안 멈추던 버그 완전 해결</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>v2.4.0</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>기능 고도화</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>app/services/mlb_service.py
+app/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>MLB 실시간 LIVE 경기 판정 정밀화 및 투수/타자 실시간 연동:
+- MLB API statusCode('O', 'F', 'CR', 'FR') 및 detailedState('Game Over') 즉시 종료 처리
+- 실시간 LIVE 이닝 포맷 한국어 정밀 매핑 (8회초 1아웃, 8회말 등)
+- 공식 linescore에서 현재 마운드 투수(current_pitcher) 및 타석 타자(current_batter) 실시간 추출하여 카드에 표출
+- 종료 경기 노출 25개, 예정 경기 16개로 확대하여 당일 전 경기 및 내일 일정 완벽 커버
+- LIVE 경기 25초, 비경기 시간대 90초 백그라운드 스마트 자동 폴링 적용</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>끝난 경기가 LIVE로 남는 현상 방지, 실시간 투수 vs 타자 매치업 카드 시각화, 당일 전 경기 스코어 열람</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
           <t>v2.3.0</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>기능 개선</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>kbo_service.py
 kleague_service.py
@@ -3264,7 +3348,7 @@
 overseas_soccer_service.py</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>스마트 캐시 갱신 구조 도입 및 LIVE 경기 안전 판별 강화:
 - 30분 TTL 캐시 유지 + 라이브 경기 시 25초 주기 실시간 fetch
@@ -3272,38 +3356,38 @@
 - 프론트엔드 30초 무중단 자동 폴링(startLivePolling)</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>종료된 경기가 LIVE로 남아있던 버그 완전 해결, 새로고침 시 실시간 최신 스코어/이닝 즉시 동기화</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>v2.3.0</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>기능 개선</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>app/services/mlb_service.py
 app/templates/index.html</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>MLB 한국 표준시(KST) 변환 &amp; 팀 ID / 네이버 연동 정상화:
 - UTC 시간의 KST 9시간 자동 변환(%m.%d HH:MM) 및 헤더 뱃지 표기
@@ -3311,38 +3395,38 @@
 - 네이버 해외야구(wbaseball) API 매핑(fetch_naver_wbaseball_map)으로 공식 gameId 확보</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>경기 시간 가독성 100% 개선 및 네이버 실시간 문자중계 gameId 100% 매핑 연동</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>v2.3.0</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>UI/UX 개선</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>app/static/js/main.js
 app/templates/index.html</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>실시간 중계 모달(live-relay-modal) UX 단독 팝업화 &amp; 바로가기 강화:
 - [실시간 중계확인] 클릭 시 새 창 동시 실행 제거 -&gt; 단독 내부 팝업으로 깔끔하게 표출
@@ -3350,39 +3434,39 @@
 - 브라우저 iframe 보안 정책으로 인한 멈춤 방어(1.5초 자동 페이드아웃)</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>새 창/팝업 이중 실행 혼란 제거, 사용자가 원하는 팝업 내 쾌적한 중계 감상</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>v2.3.0</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>버그 수정</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>app/templates/index.html
 app/templates/base.html
 overseas_soccer_service.py</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>브라우저 개발자도구 콘솔 오류 3종 완전 제거:
 1) iframe 인라인 onload 제거 및 상단 방어 선언으로 onRelayIframeLoaded is not defined 해결
@@ -3391,82 +3475,9 @@
 4) main.js?v=... 스크립트 캐시 버스팅 적용</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>F12 개발자도구 콘솔 오류 0(Zero) 무결성 확보</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>v2.2.0</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>기능 추가</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>app/templates/index.html
-app/static/js/main.js</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>네이버스포츠 실시간 문자중계 모달(live-relay-modal) 최초 구현:
-- LIVE 경기 카드에 [실시간 중계확인] 버튼 노출 및 인라인 모달 연동</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>페이지 이탈 없는 실시간 문자중계 확인 환경 제공</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>v2.1.0</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>UI 개선</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>app/templates/index.html
-app/static/css/style.css</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>상단 경기결과 / 하단 영상 레이아웃 개편 및 상태 필터 칩 고도화</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>스코어보드 시인성 향상 및 한눈에 들어오는 경기 요약</t>
         </is>
       </c>
     </row>
@@ -3476,30 +3487,103 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>v2.2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>기능 추가</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>app/templates/index.html
+app/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>네이버스포츠 실시간 문자중계 모달(live-relay-modal) 최초 구현:
+- LIVE 경기 카드에 [실시간 중계확인] 버튼 노출 및 인라인 모달 연동</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>페이지 이탈 없는 실시간 문자중계 확인 환경 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>UI 개선</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>app/templates/index.html
+app/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>상단 경기결과 / 하단 영상 레이아웃 개편 및 상태 필터 칩 고도화</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>스코어보드 시인성 향상 및 한눈에 들어오는 경기 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>v2.0.0</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>전체 프로젝트</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>4대 스포츠(KBO, K리그, 해외축구, MLB) 통합 올인원 대시보드 시스템 구축</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>종목별 분산 정보를 하나의 웹 허브로 통합</t>
         </is>
